--- a/files/九龙-启德-天玺．天.xlsx
+++ b/files/九龙-启德-天玺．天.xlsx
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1993</v>
+        <v>1921</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>83052000</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>41672</v>
+        <v>43234</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>83052000</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>41672</v>
+        <v>43234</v>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
@@ -57336,9 +57336,9 @@
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>A | 1993呎 (4+房)
+          <t>A | 1921呎 (4+房)
 $8305万
-$41,672/呎
+$43,234/呎
 (24年-11月-12日)</t>
         </is>
       </c>

--- a/files/九龙-启德-天玺．天.xlsx
+++ b/files/九龙-启德-天玺．天.xlsx
@@ -9811,7 +9811,7 @@
         </is>
       </c>
       <c r="E148" s="4" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>9504400</v>
       </c>
       <c r="I148" s="5" t="n">
-        <v>20752</v>
+        <v>20707</v>
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         <v>9504400</v>
       </c>
       <c r="L148" s="5" t="n">
-        <v>20752</v>
+        <v>20707</v>
       </c>
       <c r="M148" s="3" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
         </is>
       </c>
       <c r="E271" s="4" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F271" s="3" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>9846000</v>
       </c>
       <c r="I271" s="5" t="n">
-        <v>21498</v>
+        <v>21451</v>
       </c>
       <c r="J271" s="3" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>9846000</v>
       </c>
       <c r="L271" s="5" t="n">
-        <v>21498</v>
+        <v>21451</v>
       </c>
       <c r="M271" s="3" t="inlineStr">
         <is>
@@ -58881,9 +58881,9 @@
       <c r="G30" s="20" t="inlineStr"/>
       <c r="H30" s="22" t="inlineStr">
         <is>
-          <t>B1 | 458呎 (2房)
+          <t>B1 | 459呎 (2房)
 $950万
-$20,752/呎
+$20,707/呎
 (24年-11月-08日)</t>
         </is>
       </c>
@@ -60426,9 +60426,9 @@
       </c>
       <c r="S9" s="22" t="inlineStr">
         <is>
-          <t>F | 458呎 (2房)
+          <t>F | 459呎 (2房)
 $985万
-$21,498/呎
+$21,451/呎
 (24年-11月-05日)</t>
         </is>
       </c>

--- a/files/九龙-启德-天玺．天.xlsx
+++ b/files/九龙-启德-天玺．天.xlsx
@@ -13159,7 +13159,7 @@
         </is>
       </c>
       <c r="E202" s="4" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>9372200</v>
       </c>
       <c r="I202" s="5" t="n">
-        <v>20463</v>
+        <v>20419</v>
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         <v>9372200</v>
       </c>
       <c r="L202" s="5" t="n">
-        <v>20463</v>
+        <v>20419</v>
       </c>
       <c r="M202" s="3" t="inlineStr">
         <is>
@@ -59403,9 +59403,9 @@
       <c r="G36" s="20" t="inlineStr"/>
       <c r="H36" s="22" t="inlineStr">
         <is>
-          <t>B1 | 458呎 (2房)
+          <t>B1 | 459呎 (2房)
 $937万
-$20,463/呎
+$20,419/呎
 (24年-11月-06日)</t>
         </is>
       </c>

--- a/files/九龙-启德-天玺．天.xlsx
+++ b/files/九龙-启德-天玺．天.xlsx
@@ -9687,7 +9687,7 @@
         </is>
       </c>
       <c r="E146" s="4" t="n">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>6690100</v>
       </c>
       <c r="I146" s="5" t="n">
-        <v>22226</v>
+        <v>22300</v>
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
@@ -9714,7 +9714,7 @@
         <v>6690100</v>
       </c>
       <c r="L146" s="5" t="n">
-        <v>22226</v>
+        <v>22300</v>
       </c>
       <c r="M146" s="3" t="inlineStr">
         <is>
@@ -58897,9 +58897,9 @@
       </c>
       <c r="J30" s="22" t="inlineStr">
         <is>
-          <t>B3 | 301呎 (1房)
+          <t>B3 | 300呎 (1房)
 $669万
-$22,226/呎
+$22,300/呎
 (24年-11月-01日)</t>
         </is>
       </c>

--- a/files/九龙-启德-天玺．天.xlsx
+++ b/files/九龙-启德-天玺．天.xlsx
@@ -39333,7 +39333,7 @@
         </is>
       </c>
       <c r="E623" s="4" t="n">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="F623" s="3" t="inlineStr">
         <is>
@@ -39349,7 +39349,7 @@
         <v>30325000</v>
       </c>
       <c r="I623" s="5" t="n">
-        <v>33361</v>
+        <v>33398</v>
       </c>
       <c r="J623" s="3" t="inlineStr">
         <is>
@@ -39360,7 +39360,7 @@
         <v>30325000</v>
       </c>
       <c r="L623" s="5" t="n">
-        <v>33361</v>
+        <v>33398</v>
       </c>
       <c r="M623" s="3" t="inlineStr">
         <is>
@@ -64053,9 +64053,9 @@
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>A | 909呎 (4+房)
+          <t>A | 908呎 (4+房)
 $3032万
-$33,361/呎
+$33,398/呎
 (24年-11月-15日)</t>
         </is>
       </c>

--- a/files/九龙-启德-天玺．天.xlsx
+++ b/files/九龙-启德-天玺．天.xlsx
@@ -3239,7 +3239,7 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>1993</v>
+        <v>1921</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>69888000</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>35067</v>
+        <v>36381</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>69888000</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>35067</v>
+        <v>36381</v>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
@@ -57752,9 +57752,9 @@
       </c>
       <c r="B15" s="22" t="inlineStr">
         <is>
-          <t>A | 1993呎 (4+房)
+          <t>A | 1921呎 (4+房)
 $6989万
-$35,067/呎
+$36,381/呎
 (24年-11月-04日)</t>
         </is>
       </c>

--- a/files/九龙-启德-天玺．天.xlsx
+++ b/files/九龙-启德-天玺．天.xlsx
@@ -15701,7 +15701,7 @@
         </is>
       </c>
       <c r="E243" s="4" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>8900900</v>
       </c>
       <c r="I243" s="5" t="n">
-        <v>20368</v>
+        <v>20322</v>
       </c>
       <c r="J243" s="3" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>8900900</v>
       </c>
       <c r="L243" s="5" t="n">
-        <v>20368</v>
+        <v>20322</v>
       </c>
       <c r="M243" s="3" t="inlineStr">
         <is>
@@ -37597,7 +37597,7 @@
         </is>
       </c>
       <c r="E595" s="4" t="n">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F595" s="3" t="inlineStr">
         <is>
@@ -37613,7 +37613,7 @@
         <v>10181500</v>
       </c>
       <c r="I595" s="5" t="n">
-        <v>21709</v>
+        <v>21755</v>
       </c>
       <c r="J595" s="3" t="inlineStr">
         <is>
@@ -37624,7 +37624,7 @@
         <v>10181500</v>
       </c>
       <c r="L595" s="5" t="n">
-        <v>21709</v>
+        <v>21755</v>
       </c>
       <c r="M595" s="3" t="inlineStr">
         <is>
@@ -59870,9 +59870,9 @@
       </c>
       <c r="L41" s="22" t="inlineStr">
         <is>
-          <t>B6 | 437呎 (2房)
+          <t>B6 | 438呎 (2房)
 $890万
-$20,368/呎
+$20,322/呎
 (24年-11月-05日)</t>
         </is>
       </c>
@@ -63838,9 +63838,9 @@
       </c>
       <c r="Q7" s="22" t="inlineStr">
         <is>
-          <t>E | 469呎 (2房)
+          <t>E | 468呎 (2房)
 $1018万
-$21,709/呎
+$21,755/呎
 (24年-11月-06日)</t>
         </is>
       </c>

--- a/files/九龙-启德-天玺．天.xlsx
+++ b/files/九龙-启德-天玺．天.xlsx
@@ -4541,7 +4541,7 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>9728100</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>22261</v>
+        <v>22210</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>9728100</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>22261</v>
+        <v>22210</v>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
@@ -58130,9 +58130,9 @@
       </c>
       <c r="L21" s="22" t="inlineStr">
         <is>
-          <t>B6 | 437呎 (2房)
+          <t>B6 | 438呎 (2房)
 $973万
-$22,261/呎
+$22,210/呎
 (24年-11月-01日)</t>
         </is>
       </c>

--- a/files/九龙-启德-天玺．天.xlsx
+++ b/files/九龙-启德-天玺．天.xlsx
@@ -14833,7 +14833,7 @@
         </is>
       </c>
       <c r="E229" s="4" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
@@ -14849,7 +14849,7 @@
         <v>9187000</v>
       </c>
       <c r="I229" s="5" t="n">
-        <v>20059</v>
+        <v>20015</v>
       </c>
       <c r="J229" s="3" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>9187000</v>
       </c>
       <c r="L229" s="5" t="n">
-        <v>20059</v>
+        <v>20015</v>
       </c>
       <c r="M229" s="3" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         </is>
       </c>
       <c r="E292" s="4" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F292" s="3" t="inlineStr">
         <is>
@@ -18787,7 +18787,7 @@
         <v>9757600</v>
       </c>
       <c r="I292" s="5" t="n">
-        <v>21305</v>
+        <v>21258</v>
       </c>
       <c r="J292" s="3" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
         <v>9757600</v>
       </c>
       <c r="L292" s="5" t="n">
-        <v>21305</v>
+        <v>21258</v>
       </c>
       <c r="M292" s="3" t="inlineStr">
         <is>
@@ -59664,9 +59664,9 @@
       <c r="G39" s="20" t="inlineStr"/>
       <c r="H39" s="22" t="inlineStr">
         <is>
-          <t>B1 | 458呎 (2房)
+          <t>B1 | 459呎 (2房)
 $919万
-$20,059/呎
+$20,015/呎
 (24年-11月-08日)</t>
         </is>
       </c>
@@ -60663,9 +60663,9 @@
       </c>
       <c r="S12" s="22" t="inlineStr">
         <is>
-          <t>F | 458呎 (2房)
+          <t>F | 459呎 (2房)
 $976万
-$21,305/呎
+$21,258/呎
 (24年-11月-05日)</t>
         </is>
       </c>

--- a/files/九龙-启德-天玺．天.xlsx
+++ b/files/九龙-启德-天玺．天.xlsx
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1921</v>
+        <v>1993</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>83052000</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>43234</v>
+        <v>41672</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>83052000</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>43234</v>
+        <v>41672</v>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1153</v>
+        <v>1227</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>32580000</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>28257</v>
+        <v>26553</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>32580000</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>28257</v>
+        <v>26553</v>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1921</v>
+        <v>1993</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>80146000</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>41721</v>
+        <v>40214</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         <v>80146000</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>41721</v>
+        <v>40214</v>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1914</v>
+        <v>1985</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>77550000</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>40517</v>
+        <v>39068</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>77550000</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>40517</v>
+        <v>39068</v>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>1921</v>
+        <v>1993</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>69888000</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>36381</v>
+        <v>35067</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>69888000</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>36381</v>
+        <v>35067</v>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>1921</v>
+        <v>1993</v>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>66444000</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>34588</v>
+        <v>33339</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>66444000</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>34588</v>
+        <v>33339</v>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>1914</v>
+        <v>1985</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         <v>69899000</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>36520</v>
+        <v>35214</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>69899000</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>36520</v>
+        <v>35214</v>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>9728100</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>22210</v>
+        <v>22261</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>9728100</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>22210</v>
+        <v>22261</v>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
@@ -5781,7 +5781,7 @@
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>6811500</v>
       </c>
       <c r="I83" s="5" t="n">
-        <v>22705</v>
+        <v>22630</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>6811500</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>22705</v>
+        <v>22630</v>
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
@@ -6463,7 +6463,7 @@
         </is>
       </c>
       <c r="E94" s="4" t="n">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         <v>9676800</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>21082</v>
+        <v>21128</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>9676800</v>
       </c>
       <c r="L94" s="5" t="n">
-        <v>21082</v>
+        <v>21128</v>
       </c>
       <c r="M94" s="3" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         </is>
       </c>
       <c r="E110" s="4" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
@@ -7471,7 +7471,7 @@
         <v>6757200</v>
       </c>
       <c r="I110" s="5" t="n">
-        <v>22524</v>
+        <v>22449</v>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
@@ -7482,7 +7482,7 @@
         <v>6757200</v>
       </c>
       <c r="L110" s="5" t="n">
-        <v>22524</v>
+        <v>22449</v>
       </c>
       <c r="M110" s="3" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="E119" s="4" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
@@ -8029,7 +8029,7 @@
         <v>6737100</v>
       </c>
       <c r="I119" s="5" t="n">
-        <v>22457</v>
+        <v>22382</v>
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>6737100</v>
       </c>
       <c r="L119" s="5" t="n">
-        <v>22457</v>
+        <v>22382</v>
       </c>
       <c r="M119" s="3" t="inlineStr">
         <is>
@@ -9687,7 +9687,7 @@
         </is>
       </c>
       <c r="E146" s="4" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>6690100</v>
       </c>
       <c r="I146" s="5" t="n">
-        <v>22300</v>
+        <v>22226</v>
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
@@ -9714,7 +9714,7 @@
         <v>6690100</v>
       </c>
       <c r="L146" s="5" t="n">
-        <v>22300</v>
+        <v>22226</v>
       </c>
       <c r="M146" s="3" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         </is>
       </c>
       <c r="E148" s="4" t="n">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>9504400</v>
       </c>
       <c r="I148" s="5" t="n">
-        <v>20707</v>
+        <v>20752</v>
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         <v>9504400</v>
       </c>
       <c r="L148" s="5" t="n">
-        <v>20707</v>
+        <v>20752</v>
       </c>
       <c r="M148" s="3" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         </is>
       </c>
       <c r="E153" s="4" t="n">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>9347600</v>
       </c>
       <c r="I153" s="5" t="n">
-        <v>21342</v>
+        <v>21390</v>
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
@@ -10148,7 +10148,7 @@
         <v>9347600</v>
       </c>
       <c r="L153" s="5" t="n">
-        <v>21342</v>
+        <v>21390</v>
       </c>
       <c r="M153" s="3" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         </is>
       </c>
       <c r="E155" s="4" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>6676800</v>
       </c>
       <c r="I155" s="5" t="n">
-        <v>22256</v>
+        <v>22182</v>
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>6676800</v>
       </c>
       <c r="L155" s="5" t="n">
-        <v>22256</v>
+        <v>22182</v>
       </c>
       <c r="M155" s="3" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
         </is>
       </c>
       <c r="E182" s="4" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>6636800</v>
       </c>
       <c r="I182" s="5" t="n">
-        <v>22123</v>
+        <v>22049</v>
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
@@ -11946,7 +11946,7 @@
         <v>6636800</v>
       </c>
       <c r="L182" s="5" t="n">
-        <v>22123</v>
+        <v>22049</v>
       </c>
       <c r="M182" s="3" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         </is>
       </c>
       <c r="E200" s="4" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
@@ -13051,7 +13051,7 @@
         <v>6597000</v>
       </c>
       <c r="I200" s="5" t="n">
-        <v>21990</v>
+        <v>21917</v>
       </c>
       <c r="J200" s="3" t="inlineStr">
         <is>
@@ -13062,7 +13062,7 @@
         <v>6597000</v>
       </c>
       <c r="L200" s="5" t="n">
-        <v>21990</v>
+        <v>21917</v>
       </c>
       <c r="M200" s="3" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
         </is>
       </c>
       <c r="E202" s="4" t="n">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>9372200</v>
       </c>
       <c r="I202" s="5" t="n">
-        <v>20419</v>
+        <v>20463</v>
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         <v>9372200</v>
       </c>
       <c r="L202" s="5" t="n">
-        <v>20419</v>
+        <v>20463</v>
       </c>
       <c r="M202" s="3" t="inlineStr">
         <is>
@@ -13593,7 +13593,7 @@
         </is>
       </c>
       <c r="E209" s="4" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>6577200</v>
       </c>
       <c r="I209" s="5" t="n">
-        <v>21924</v>
+        <v>21851</v>
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
@@ -13620,7 +13620,7 @@
         <v>6577200</v>
       </c>
       <c r="L209" s="5" t="n">
-        <v>21924</v>
+        <v>21851</v>
       </c>
       <c r="M209" s="3" t="inlineStr">
         <is>
@@ -14151,7 +14151,7 @@
         </is>
       </c>
       <c r="E218" s="4" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
@@ -14167,7 +14167,7 @@
         <v>6518200</v>
       </c>
       <c r="I218" s="5" t="n">
-        <v>21727</v>
+        <v>21655</v>
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
@@ -14178,7 +14178,7 @@
         <v>6518200</v>
       </c>
       <c r="L218" s="5" t="n">
-        <v>21727</v>
+        <v>21655</v>
       </c>
       <c r="M218" s="3" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         </is>
       </c>
       <c r="E225" s="4" t="n">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
@@ -14601,7 +14601,7 @@
         <v>9053400</v>
       </c>
       <c r="I225" s="5" t="n">
-        <v>20670</v>
+        <v>20717</v>
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
@@ -14612,7 +14612,7 @@
         <v>9053400</v>
       </c>
       <c r="L225" s="5" t="n">
-        <v>20670</v>
+        <v>20717</v>
       </c>
       <c r="M225" s="3" t="inlineStr">
         <is>
@@ -14833,7 +14833,7 @@
         </is>
       </c>
       <c r="E229" s="4" t="n">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
@@ -14849,7 +14849,7 @@
         <v>9187000</v>
       </c>
       <c r="I229" s="5" t="n">
-        <v>20015</v>
+        <v>20059</v>
       </c>
       <c r="J229" s="3" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>9187000</v>
       </c>
       <c r="L229" s="5" t="n">
-        <v>20015</v>
+        <v>20059</v>
       </c>
       <c r="M229" s="3" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         </is>
       </c>
       <c r="E236" s="4" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
@@ -15283,7 +15283,7 @@
         <v>6380800</v>
       </c>
       <c r="I236" s="5" t="n">
-        <v>21269</v>
+        <v>21199</v>
       </c>
       <c r="J236" s="3" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
         <v>6380800</v>
       </c>
       <c r="L236" s="5" t="n">
-        <v>21269</v>
+        <v>21199</v>
       </c>
       <c r="M236" s="3" t="inlineStr">
         <is>
@@ -15391,7 +15391,7 @@
         </is>
       </c>
       <c r="E238" s="4" t="n">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>9057800</v>
       </c>
       <c r="I238" s="5" t="n">
-        <v>19734</v>
+        <v>19777</v>
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
@@ -15418,7 +15418,7 @@
         <v>9057800</v>
       </c>
       <c r="L238" s="5" t="n">
-        <v>19734</v>
+        <v>19777</v>
       </c>
       <c r="M238" s="3" t="inlineStr">
         <is>
@@ -15701,7 +15701,7 @@
         </is>
       </c>
       <c r="E243" s="4" t="n">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>8900900</v>
       </c>
       <c r="I243" s="5" t="n">
-        <v>20322</v>
+        <v>20368</v>
       </c>
       <c r="J243" s="3" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>8900900</v>
       </c>
       <c r="L243" s="5" t="n">
-        <v>20322</v>
+        <v>20368</v>
       </c>
       <c r="M243" s="3" t="inlineStr">
         <is>
@@ -15949,7 +15949,7 @@
         </is>
       </c>
       <c r="E247" s="4" t="n">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F247" s="3" t="inlineStr">
         <is>
@@ -15965,7 +15965,7 @@
         <v>8740800</v>
       </c>
       <c r="I247" s="5" t="n">
-        <v>19043</v>
+        <v>19085</v>
       </c>
       <c r="J247" s="3" t="inlineStr">
         <is>
@@ -15976,7 +15976,7 @@
         <v>8740800</v>
       </c>
       <c r="L247" s="5" t="n">
-        <v>19043</v>
+        <v>19085</v>
       </c>
       <c r="M247" s="3" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         </is>
       </c>
       <c r="E264" s="4" t="n">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F264" s="3" t="inlineStr">
         <is>
@@ -17051,7 +17051,7 @@
         <v>9875500</v>
       </c>
       <c r="I264" s="5" t="n">
-        <v>21515</v>
+        <v>21562</v>
       </c>
       <c r="J264" s="3" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>9875500</v>
       </c>
       <c r="L264" s="5" t="n">
-        <v>21515</v>
+        <v>21562</v>
       </c>
       <c r="M264" s="3" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
         </is>
       </c>
       <c r="E271" s="4" t="n">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F271" s="3" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>9846000</v>
       </c>
       <c r="I271" s="5" t="n">
-        <v>21451</v>
+        <v>21498</v>
       </c>
       <c r="J271" s="3" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>9846000</v>
       </c>
       <c r="L271" s="5" t="n">
-        <v>21451</v>
+        <v>21498</v>
       </c>
       <c r="M271" s="3" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         </is>
       </c>
       <c r="E292" s="4" t="n">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F292" s="3" t="inlineStr">
         <is>
@@ -18787,7 +18787,7 @@
         <v>9757600</v>
       </c>
       <c r="I292" s="5" t="n">
-        <v>21258</v>
+        <v>21305</v>
       </c>
       <c r="J292" s="3" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
         <v>9757600</v>
       </c>
       <c r="L292" s="5" t="n">
-        <v>21258</v>
+        <v>21305</v>
       </c>
       <c r="M292" s="3" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         </is>
       </c>
       <c r="E310" s="4" t="n">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="F310" s="3" t="inlineStr">
         <is>
@@ -19919,7 +19919,7 @@
         <v>18513700</v>
       </c>
       <c r="I310" s="5" t="n">
-        <v>26949</v>
+        <v>26988</v>
       </c>
       <c r="J310" s="3" t="inlineStr">
         <is>
@@ -19930,7 +19930,7 @@
         <v>18513700</v>
       </c>
       <c r="L310" s="5" t="n">
-        <v>26949</v>
+        <v>26988</v>
       </c>
       <c r="M310" s="3" t="inlineStr">
         <is>
@@ -21267,7 +21267,7 @@
         </is>
       </c>
       <c r="E332" s="4" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F332" s="3" t="inlineStr">
         <is>
@@ -21283,7 +21283,7 @@
         <v>7405300</v>
       </c>
       <c r="I332" s="5" t="n">
-        <v>24850</v>
+        <v>24767</v>
       </c>
       <c r="J332" s="3" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>7405300</v>
       </c>
       <c r="L332" s="5" t="n">
-        <v>24850</v>
+        <v>24767</v>
       </c>
       <c r="M332" s="3" t="inlineStr">
         <is>
@@ -22073,7 +22073,7 @@
         </is>
       </c>
       <c r="E345" s="4" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F345" s="3" t="inlineStr">
         <is>
@@ -22089,7 +22089,7 @@
         <v>7398200</v>
       </c>
       <c r="I345" s="5" t="n">
-        <v>24826</v>
+        <v>24743</v>
       </c>
       <c r="J345" s="3" t="inlineStr">
         <is>
@@ -22100,7 +22100,7 @@
         <v>7398200</v>
       </c>
       <c r="L345" s="5" t="n">
-        <v>24826</v>
+        <v>24743</v>
       </c>
       <c r="M345" s="3" t="inlineStr">
         <is>
@@ -22631,7 +22631,7 @@
         </is>
       </c>
       <c r="E354" s="4" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F354" s="3" t="inlineStr">
         <is>
@@ -22647,7 +22647,7 @@
         <v>11132100</v>
       </c>
       <c r="I354" s="5" t="n">
-        <v>21914</v>
+        <v>21871</v>
       </c>
       <c r="J354" s="3" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>11132100</v>
       </c>
       <c r="L354" s="5" t="n">
-        <v>21914</v>
+        <v>21871</v>
       </c>
       <c r="M354" s="3" t="inlineStr">
         <is>
@@ -24243,7 +24243,7 @@
         </is>
       </c>
       <c r="E380" s="4" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F380" s="3" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>7366600</v>
       </c>
       <c r="I380" s="5" t="n">
-        <v>24720</v>
+        <v>24637</v>
       </c>
       <c r="J380" s="3" t="inlineStr">
         <is>
@@ -24270,7 +24270,7 @@
         <v>7366600</v>
       </c>
       <c r="L380" s="5" t="n">
-        <v>24720</v>
+        <v>24637</v>
       </c>
       <c r="M380" s="3" t="inlineStr">
         <is>
@@ -27839,7 +27839,7 @@
         </is>
       </c>
       <c r="E438" s="4" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F438" s="3" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>10851100</v>
       </c>
       <c r="I438" s="5" t="n">
-        <v>21360</v>
+        <v>21318</v>
       </c>
       <c r="J438" s="3" t="inlineStr">
         <is>
@@ -27866,7 +27866,7 @@
         <v>10851100</v>
       </c>
       <c r="L438" s="5" t="n">
-        <v>21360</v>
+        <v>21318</v>
       </c>
       <c r="M438" s="3" t="inlineStr">
         <is>
@@ -27963,7 +27963,7 @@
         </is>
       </c>
       <c r="E440" s="4" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F440" s="3" t="inlineStr">
         <is>
@@ -27979,7 +27979,7 @@
         <v>7410400</v>
       </c>
       <c r="I440" s="5" t="n">
-        <v>24867</v>
+        <v>24784</v>
       </c>
       <c r="J440" s="3" t="inlineStr">
         <is>
@@ -27990,7 +27990,7 @@
         <v>7410400</v>
       </c>
       <c r="L440" s="5" t="n">
-        <v>24867</v>
+        <v>24784</v>
       </c>
       <c r="M440" s="3" t="inlineStr">
         <is>
@@ -28583,7 +28583,7 @@
         </is>
       </c>
       <c r="E450" s="4" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F450" s="3" t="inlineStr">
         <is>
@@ -28599,7 +28599,7 @@
         <v>10839400</v>
       </c>
       <c r="I450" s="5" t="n">
-        <v>21337</v>
+        <v>21295</v>
       </c>
       <c r="J450" s="3" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>10839400</v>
       </c>
       <c r="L450" s="5" t="n">
-        <v>21337</v>
+        <v>21295</v>
       </c>
       <c r="M450" s="3" t="inlineStr">
         <is>
@@ -29327,7 +29327,7 @@
         </is>
       </c>
       <c r="E462" s="4" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F462" s="3" t="inlineStr">
         <is>
@@ -29343,7 +29343,7 @@
         <v>10817800</v>
       </c>
       <c r="I462" s="5" t="n">
-        <v>21295</v>
+        <v>21253</v>
       </c>
       <c r="J462" s="3" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
         <v>10817800</v>
       </c>
       <c r="L462" s="5" t="n">
-        <v>21295</v>
+        <v>21253</v>
       </c>
       <c r="M462" s="3" t="inlineStr">
         <is>
@@ -29513,7 +29513,7 @@
         </is>
       </c>
       <c r="E465" s="4" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F465" s="3" t="inlineStr">
         <is>
@@ -29529,7 +29529,7 @@
         <v>7380900</v>
       </c>
       <c r="I465" s="5" t="n">
-        <v>24768</v>
+        <v>24685</v>
       </c>
       <c r="J465" s="3" t="inlineStr">
         <is>
@@ -29540,7 +29540,7 @@
         <v>7380900</v>
       </c>
       <c r="L465" s="5" t="n">
-        <v>24768</v>
+        <v>24685</v>
       </c>
       <c r="M465" s="3" t="inlineStr">
         <is>
@@ -31001,7 +31001,7 @@
         </is>
       </c>
       <c r="E489" s="4" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F489" s="3" t="inlineStr">
         <is>
@@ -31017,7 +31017,7 @@
         <v>7351300</v>
       </c>
       <c r="I489" s="5" t="n">
-        <v>24669</v>
+        <v>24586</v>
       </c>
       <c r="J489" s="3" t="inlineStr">
         <is>
@@ -31028,7 +31028,7 @@
         <v>7351300</v>
       </c>
       <c r="L489" s="5" t="n">
-        <v>24669</v>
+        <v>24586</v>
       </c>
       <c r="M489" s="3" t="inlineStr">
         <is>
@@ -32489,7 +32489,7 @@
         </is>
       </c>
       <c r="E513" s="4" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F513" s="3" t="inlineStr">
         <is>
@@ -32505,7 +32505,7 @@
         <v>7314600</v>
       </c>
       <c r="I513" s="5" t="n">
-        <v>24546</v>
+        <v>24464</v>
       </c>
       <c r="J513" s="3" t="inlineStr">
         <is>
@@ -32516,7 +32516,7 @@
         <v>7314600</v>
       </c>
       <c r="L513" s="5" t="n">
-        <v>24546</v>
+        <v>24464</v>
       </c>
       <c r="M513" s="3" t="inlineStr">
         <is>
@@ -36209,7 +36209,7 @@
         </is>
       </c>
       <c r="E573" s="4" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F573" s="3" t="inlineStr">
         <is>
@@ -36225,7 +36225,7 @@
         <v>6555000</v>
       </c>
       <c r="I573" s="5" t="n">
-        <v>21997</v>
+        <v>21923</v>
       </c>
       <c r="J573" s="3" t="inlineStr">
         <is>
@@ -36236,7 +36236,7 @@
         <v>6555000</v>
       </c>
       <c r="L573" s="5" t="n">
-        <v>21997</v>
+        <v>21923</v>
       </c>
       <c r="M573" s="3" t="inlineStr">
         <is>
@@ -36891,7 +36891,7 @@
         </is>
       </c>
       <c r="E584" s="4" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F584" s="3" t="inlineStr">
         <is>
@@ -36907,7 +36907,7 @@
         <v>5768400</v>
       </c>
       <c r="I584" s="5" t="n">
-        <v>19357</v>
+        <v>19292</v>
       </c>
       <c r="J584" s="3" t="inlineStr">
         <is>
@@ -36918,7 +36918,7 @@
         <v>5768400</v>
       </c>
       <c r="L584" s="5" t="n">
-        <v>19357</v>
+        <v>19292</v>
       </c>
       <c r="M584" s="3" t="inlineStr">
         <is>
@@ -37597,7 +37597,7 @@
         </is>
       </c>
       <c r="E595" s="4" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F595" s="3" t="inlineStr">
         <is>
@@ -37613,7 +37613,7 @@
         <v>10181500</v>
       </c>
       <c r="I595" s="5" t="n">
-        <v>21755</v>
+        <v>21709</v>
       </c>
       <c r="J595" s="3" t="inlineStr">
         <is>
@@ -37624,7 +37624,7 @@
         <v>10181500</v>
       </c>
       <c r="L595" s="5" t="n">
-        <v>21755</v>
+        <v>21709</v>
       </c>
       <c r="M595" s="3" t="inlineStr">
         <is>
@@ -39333,7 +39333,7 @@
         </is>
       </c>
       <c r="E623" s="4" t="n">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="F623" s="3" t="inlineStr">
         <is>
@@ -39349,7 +39349,7 @@
         <v>30325000</v>
       </c>
       <c r="I623" s="5" t="n">
-        <v>33398</v>
+        <v>33361</v>
       </c>
       <c r="J623" s="3" t="inlineStr">
         <is>
@@ -39360,7 +39360,7 @@
         <v>30325000</v>
       </c>
       <c r="L623" s="5" t="n">
-        <v>33398</v>
+        <v>33361</v>
       </c>
       <c r="M623" s="3" t="inlineStr">
         <is>
@@ -39519,7 +39519,7 @@
         </is>
       </c>
       <c r="E626" s="4" t="n">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F626" s="3" t="inlineStr">
         <is>
@@ -39535,7 +39535,7 @@
         <v>10129000</v>
       </c>
       <c r="I626" s="5" t="n">
-        <v>21972</v>
+        <v>22020</v>
       </c>
       <c r="J626" s="3" t="inlineStr">
         <is>
@@ -39546,7 +39546,7 @@
         <v>10129000</v>
       </c>
       <c r="L626" s="5" t="n">
-        <v>21972</v>
+        <v>22020</v>
       </c>
       <c r="M626" s="3" t="inlineStr">
         <is>
@@ -41069,7 +41069,7 @@
         </is>
       </c>
       <c r="E651" s="4" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F651" s="3" t="inlineStr">
         <is>
@@ -41085,7 +41085,7 @@
         <v>10302100</v>
       </c>
       <c r="I651" s="5" t="n">
-        <v>22013</v>
+        <v>21966</v>
       </c>
       <c r="J651" s="3" t="inlineStr">
         <is>
@@ -41096,7 +41096,7 @@
         <v>10302100</v>
       </c>
       <c r="L651" s="5" t="n">
-        <v>22013</v>
+        <v>21966</v>
       </c>
       <c r="M651" s="3" t="inlineStr">
         <is>
@@ -42565,7 +42565,7 @@
         </is>
       </c>
       <c r="E675" s="4" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F675" s="3" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>7657300</v>
       </c>
       <c r="I675" s="5" t="n">
-        <v>25696</v>
+        <v>25610</v>
       </c>
       <c r="J675" s="3" t="inlineStr">
         <is>
@@ -42592,7 +42592,7 @@
         <v>7657300</v>
       </c>
       <c r="L675" s="5" t="n">
-        <v>25696</v>
+        <v>25610</v>
       </c>
       <c r="M675" s="3" t="inlineStr">
         <is>
@@ -45541,7 +45541,7 @@
         </is>
       </c>
       <c r="E723" s="4" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F723" s="3" t="inlineStr">
         <is>
@@ -45557,7 +45557,7 @@
         <v>5439100</v>
       </c>
       <c r="I723" s="5" t="n">
-        <v>22950</v>
+        <v>23047</v>
       </c>
       <c r="J723" s="3" t="inlineStr">
         <is>
@@ -45568,7 +45568,7 @@
         <v>5439100</v>
       </c>
       <c r="L723" s="5" t="n">
-        <v>22950</v>
+        <v>23047</v>
       </c>
       <c r="M723" s="3" t="inlineStr">
         <is>
@@ -48021,7 +48021,7 @@
         </is>
       </c>
       <c r="E763" s="4" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F763" s="3" t="inlineStr">
         <is>
@@ -48037,7 +48037,7 @@
         <v>7312300</v>
       </c>
       <c r="I763" s="5" t="n">
-        <v>24538</v>
+        <v>24456</v>
       </c>
       <c r="J763" s="3" t="inlineStr">
         <is>
@@ -48048,7 +48048,7 @@
         <v>7312300</v>
       </c>
       <c r="L763" s="5" t="n">
-        <v>24538</v>
+        <v>24456</v>
       </c>
       <c r="M763" s="3" t="inlineStr">
         <is>
@@ -48951,7 +48951,7 @@
         </is>
       </c>
       <c r="E778" s="4" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F778" s="3" t="inlineStr">
         <is>
@@ -48967,7 +48967,7 @@
         <v>5369300</v>
       </c>
       <c r="I778" s="5" t="n">
-        <v>22655</v>
+        <v>22751</v>
       </c>
       <c r="J778" s="3" t="inlineStr">
         <is>
@@ -48978,7 +48978,7 @@
         <v>5369300</v>
       </c>
       <c r="L778" s="5" t="n">
-        <v>22655</v>
+        <v>22751</v>
       </c>
       <c r="M778" s="3" t="inlineStr">
         <is>
@@ -50315,7 +50315,7 @@
         </is>
       </c>
       <c r="E800" s="4" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F800" s="3" t="inlineStr">
         <is>
@@ -50331,7 +50331,7 @@
         <v>5347900</v>
       </c>
       <c r="I800" s="5" t="n">
-        <v>22565</v>
+        <v>22661</v>
       </c>
       <c r="J800" s="3" t="inlineStr">
         <is>
@@ -50342,7 +50342,7 @@
         <v>5347900</v>
       </c>
       <c r="L800" s="5" t="n">
-        <v>22565</v>
+        <v>22661</v>
       </c>
       <c r="M800" s="3" t="inlineStr">
         <is>
@@ -52361,7 +52361,7 @@
         </is>
       </c>
       <c r="E833" s="4" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F833" s="3" t="inlineStr">
         <is>
@@ -52377,7 +52377,7 @@
         <v>5310800</v>
       </c>
       <c r="I833" s="5" t="n">
-        <v>22408</v>
+        <v>22503</v>
       </c>
       <c r="J833" s="3" t="inlineStr">
         <is>
@@ -52388,7 +52388,7 @@
         <v>5310800</v>
       </c>
       <c r="L833" s="5" t="n">
-        <v>22408</v>
+        <v>22503</v>
       </c>
       <c r="M833" s="3" t="inlineStr">
         <is>
@@ -55523,7 +55523,7 @@
         </is>
       </c>
       <c r="E884" s="4" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F884" s="3" t="inlineStr">
         <is>
@@ -55539,7 +55539,7 @@
         <v>6825900</v>
       </c>
       <c r="I884" s="5" t="n">
-        <v>22906</v>
+        <v>22829</v>
       </c>
       <c r="J884" s="3" t="inlineStr">
         <is>
@@ -55550,7 +55550,7 @@
         <v>6825900</v>
       </c>
       <c r="L884" s="5" t="n">
-        <v>22906</v>
+        <v>22829</v>
       </c>
       <c r="M884" s="3" t="inlineStr">
         <is>
@@ -57336,9 +57336,9 @@
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>A | 1921呎 (4+房)
+          <t>A | 1993呎 (4+房)
 $8305万
-$43,234/呎
+$41,672/呎
 (24年-11月-12日)</t>
         </is>
       </c>
@@ -57473,9 +57473,9 @@
       </c>
       <c r="N9" s="22" t="inlineStr">
         <is>
-          <t>D | 1153呎 (4+房)
+          <t>D | 1227呎 (4+房)
 $3258万
-$28,257/呎
+$26,553/呎
 (24年-11月-08日)</t>
         </is>
       </c>
@@ -57492,9 +57492,9 @@
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>A | 1921呎 (4+房)
+          <t>A | 1993呎 (4+房)
 $8015万
-$41,721/呎
+$40,214/呎
 (24年-10月-30日)</t>
         </is>
       </c>
@@ -57556,9 +57556,9 @@
       <c r="F11" s="20" t="inlineStr"/>
       <c r="G11" s="22" t="inlineStr">
         <is>
-          <t>B | 1914呎 (4+房)
+          <t>B | 1985呎 (4+房)
 $7755万
-$40,517/呎
+$39,068/呎
 (24年-12月-09日)</t>
         </is>
       </c>
@@ -57752,9 +57752,9 @@
       </c>
       <c r="B15" s="22" t="inlineStr">
         <is>
-          <t>A | 1921呎 (4+房)
+          <t>A | 1993呎 (4+房)
 $6989万
-$36,381/呎
+$35,067/呎
 (24年-11月-04日)</t>
         </is>
       </c>
@@ -57960,9 +57960,9 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>A | 1921呎 (4+房)
+          <t>A | 1993呎 (4+房)
 $6644万
-$34,588/呎
+$33,339/呎
 (24年-11月-14日)</t>
         </is>
       </c>
@@ -58024,9 +58024,9 @@
       <c r="F20" s="20" t="inlineStr"/>
       <c r="G20" s="22" t="inlineStr">
         <is>
-          <t>B | 1914呎 (4+房)
+          <t>B | 1985呎 (4+房)
 $6990万
-$36,520/呎
+$35,214/呎
 (24年-11月-05日)</t>
         </is>
       </c>
@@ -58130,9 +58130,9 @@
       </c>
       <c r="L21" s="22" t="inlineStr">
         <is>
-          <t>B6 | 438呎 (2房)
+          <t>B6 | 437呎 (2房)
 $973万
-$22,210/呎
+$22,261/呎
 (24年-11月-01日)</t>
         </is>
       </c>
@@ -58288,9 +58288,9 @@
       </c>
       <c r="J23" s="22" t="inlineStr">
         <is>
-          <t>B3 | 300呎 (1房)
+          <t>B3 | 301呎 (1房)
 $681万
-$22,705/呎
+$22,630/呎
 (24年-10月-31日)</t>
         </is>
       </c>
@@ -58359,9 +58359,9 @@
       <c r="G24" s="20" t="inlineStr"/>
       <c r="H24" s="22" t="inlineStr">
         <is>
-          <t>B1 | 459呎 (2房)
+          <t>B1 | 458呎 (2房)
 $968万
-$21,082/呎
+$21,128/呎
 (24年-11月-06日)</t>
         </is>
       </c>
@@ -58549,9 +58549,9 @@
       </c>
       <c r="J26" s="22" t="inlineStr">
         <is>
-          <t>B3 | 300呎 (1房)
+          <t>B3 | 301呎 (1房)
 $676万
-$22,524/呎
+$22,449/呎
 (24年-11月-04日)</t>
         </is>
       </c>
@@ -58636,9 +58636,9 @@
       </c>
       <c r="J27" s="22" t="inlineStr">
         <is>
-          <t>B3 | 300呎 (1房)
+          <t>B3 | 301呎 (1房)
 $674万
-$22,457/呎
+$22,382/呎
 (24年-11月-05日)</t>
         </is>
       </c>
@@ -58881,9 +58881,9 @@
       <c r="G30" s="20" t="inlineStr"/>
       <c r="H30" s="22" t="inlineStr">
         <is>
-          <t>B1 | 459呎 (2房)
+          <t>B1 | 458呎 (2房)
 $950万
-$20,707/呎
+$20,752/呎
 (24年-11月-08日)</t>
         </is>
       </c>
@@ -58897,9 +58897,9 @@
       </c>
       <c r="J30" s="22" t="inlineStr">
         <is>
-          <t>B3 | 300呎 (1房)
+          <t>B3 | 301呎 (1房)
 $669万
-$22,300/呎
+$22,226/呎
 (24年-11月-01日)</t>
         </is>
       </c>
@@ -58984,9 +58984,9 @@
       </c>
       <c r="J31" s="22" t="inlineStr">
         <is>
-          <t>B3 | 300呎 (1房)
+          <t>B3 | 301呎 (1房)
 $668万
-$22,256/呎
+$22,182/呎
 (24年-11月-05日)</t>
         </is>
       </c>
@@ -59000,9 +59000,9 @@
       </c>
       <c r="L31" s="22" t="inlineStr">
         <is>
-          <t>B6 | 438呎 (2房)
+          <t>B6 | 437呎 (2房)
 $935万
-$21,342/呎
+$21,390/呎
 (24年-11月-04日)</t>
         </is>
       </c>
@@ -59245,9 +59245,9 @@
       </c>
       <c r="J34" s="22" t="inlineStr">
         <is>
-          <t>B3 | 300呎 (1房)
+          <t>B3 | 301呎 (1房)
 $664万
-$22,123/呎
+$22,049/呎
 (24年-11月-01日)</t>
         </is>
       </c>
@@ -59403,9 +59403,9 @@
       <c r="G36" s="20" t="inlineStr"/>
       <c r="H36" s="22" t="inlineStr">
         <is>
-          <t>B1 | 459呎 (2房)
+          <t>B1 | 458呎 (2房)
 $937万
-$20,419/呎
+$20,463/呎
 (24年-11月-06日)</t>
         </is>
       </c>
@@ -59419,9 +59419,9 @@
       </c>
       <c r="J36" s="22" t="inlineStr">
         <is>
-          <t>B3 | 300呎 (1房)
+          <t>B3 | 301呎 (1房)
 $660万
-$21,990/呎
+$21,917/呎
 (24年-10月-29日)</t>
         </is>
       </c>
@@ -59506,9 +59506,9 @@
       </c>
       <c r="J37" s="22" t="inlineStr">
         <is>
-          <t>B3 | 300呎 (1房)
+          <t>B3 | 301呎 (1房)
 $658万
-$21,924/呎
+$21,851/呎
 (24年-10月-30日)</t>
         </is>
       </c>
@@ -59593,9 +59593,9 @@
       </c>
       <c r="J38" s="22" t="inlineStr">
         <is>
-          <t>B3 | 300呎 (1房)
+          <t>B3 | 301呎 (1房)
 $652万
-$21,727/呎
+$21,655/呎
 (24年-11月-01日)</t>
         </is>
       </c>
@@ -59664,9 +59664,9 @@
       <c r="G39" s="20" t="inlineStr"/>
       <c r="H39" s="22" t="inlineStr">
         <is>
-          <t>B1 | 459呎 (2房)
+          <t>B1 | 458呎 (2房)
 $919万
-$20,015/呎
+$20,059/呎
 (24年-11月-08日)</t>
         </is>
       </c>
@@ -59696,9 +59696,9 @@
       </c>
       <c r="L39" s="22" t="inlineStr">
         <is>
-          <t>B6 | 438呎 (2房)
+          <t>B6 | 437呎 (2房)
 $905万
-$20,670/呎
+$20,717/呎
 (24年-11月-07日)</t>
         </is>
       </c>
@@ -59751,9 +59751,9 @@
       <c r="G40" s="20" t="inlineStr"/>
       <c r="H40" s="22" t="inlineStr">
         <is>
-          <t>B1 | 459呎 (2房)
+          <t>B1 | 458呎 (2房)
 $906万
-$19,734/呎
+$19,777/呎
 (24年-11月-08日)</t>
         </is>
       </c>
@@ -59767,9 +59767,9 @@
       </c>
       <c r="J40" s="22" t="inlineStr">
         <is>
-          <t>B3 | 300呎 (1房)
+          <t>B3 | 301呎 (1房)
 $638万
-$21,269/呎
+$21,199/呎
 (24年-11月-05日)</t>
         </is>
       </c>
@@ -59838,9 +59838,9 @@
       <c r="G41" s="20" t="inlineStr"/>
       <c r="H41" s="22" t="inlineStr">
         <is>
-          <t>B1 | 459呎 (2房)
+          <t>B1 | 458呎 (2房)
 $874万
-$19,043/呎
+$19,085/呎
 (24年-11月-11日)</t>
         </is>
       </c>
@@ -59870,9 +59870,9 @@
       </c>
       <c r="L41" s="22" t="inlineStr">
         <is>
-          <t>B6 | 438呎 (2房)
+          <t>B6 | 437呎 (2房)
 $890万
-$20,322/呎
+$20,368/呎
 (24年-11月-05日)</t>
         </is>
       </c>
@@ -60347,9 +60347,9 @@
       </c>
       <c r="S8" s="22" t="inlineStr">
         <is>
-          <t>F | 459呎 (2房)
+          <t>F | 458呎 (2房)
 $988万
-$21,515/呎
+$21,562/呎
 (24年-11月-01日)</t>
         </is>
       </c>
@@ -60426,9 +60426,9 @@
       </c>
       <c r="S9" s="22" t="inlineStr">
         <is>
-          <t>F | 459呎 (2房)
+          <t>F | 458呎 (2房)
 $985万
-$21,451/呎
+$21,498/呎
 (24年-11月-05日)</t>
         </is>
       </c>
@@ -60663,9 +60663,9 @@
       </c>
       <c r="S12" s="22" t="inlineStr">
         <is>
-          <t>F | 459呎 (2房)
+          <t>F | 458呎 (2房)
 $976万
-$21,258/呎
+$21,305/呎
 (24年-11月-05日)</t>
         </is>
       </c>
@@ -60783,9 +60783,9 @@
       <c r="H14" s="20" t="inlineStr"/>
       <c r="I14" s="22" t="inlineStr">
         <is>
-          <t>B | 687呎 (3房)
+          <t>B | 686呎 (3房)
 $1851万
-$26,949/呎
+$26,988/呎
 (24年-11月-12日)</t>
         </is>
       </c>
@@ -60987,9 +60987,9 @@
       </c>
       <c r="F16" s="22" t="inlineStr">
         <is>
-          <t>A5 | 298呎 (1房)
+          <t>A5 | 299呎 (1房)
 $741万
-$24,850/呎
+$24,767/呎
 (24年-11月-01日)</t>
         </is>
       </c>
@@ -61093,9 +61093,9 @@
       </c>
       <c r="E17" s="22" t="inlineStr">
         <is>
-          <t>A3 | 298呎 (1房)
+          <t>A3 | 299呎 (1房)
 $740万
-$24,826/呎
+$24,743/呎
 (24年-10月-31日)</t>
         </is>
       </c>
@@ -61231,9 +61231,9 @@
       </c>
       <c r="H18" s="22" t="inlineStr">
         <is>
-          <t>A8 | 508呎 (2房)
+          <t>A8 | 509呎 (2房)
 $1113万
-$21,914/呎
+$21,871/呎
 (24年-10月-25日)</t>
         </is>
       </c>
@@ -61443,9 +61443,9 @@
       </c>
       <c r="F20" s="22" t="inlineStr">
         <is>
-          <t>A5 | 298呎 (1房)
+          <t>A5 | 299呎 (1房)
 $737万
-$24,720/呎
+$24,637/呎
 (24年-10月-28日)</t>
         </is>
       </c>
@@ -62013,9 +62013,9 @@
       </c>
       <c r="F25" s="22" t="inlineStr">
         <is>
-          <t>A5 | 298呎 (1房)
+          <t>A5 | 299呎 (1房)
 $741万
-$24,867/呎
+$24,784/呎
 (24年-11月-08日)</t>
         </is>
       </c>
@@ -62029,9 +62029,9 @@
       </c>
       <c r="H25" s="22" t="inlineStr">
         <is>
-          <t>A8 | 508呎 (2房)
+          <t>A8 | 509呎 (2房)
 $1085万
-$21,360/呎
+$21,318/呎
 (24年-10月-31日)</t>
         </is>
       </c>
@@ -62143,9 +62143,9 @@
       </c>
       <c r="H26" s="22" t="inlineStr">
         <is>
-          <t>A8 | 508呎 (2房)
+          <t>A8 | 509呎 (2房)
 $1084万
-$21,337/呎
+$21,295/呎
 (24年-10月-30日)</t>
         </is>
       </c>
@@ -62233,9 +62233,9 @@
       </c>
       <c r="E27" s="22" t="inlineStr">
         <is>
-          <t>A3 | 298呎 (1房)
+          <t>A3 | 299呎 (1房)
 $738万
-$24,768/呎
+$24,685/呎
 (24年-11月-11日)</t>
         </is>
       </c>
@@ -62257,9 +62257,9 @@
       </c>
       <c r="H27" s="22" t="inlineStr">
         <is>
-          <t>A8 | 508呎 (2房)
+          <t>A8 | 509呎 (2房)
 $1082万
-$21,295/呎
+$21,253/呎
 (24年-10月-25日)</t>
         </is>
       </c>
@@ -62461,9 +62461,9 @@
       </c>
       <c r="E29" s="22" t="inlineStr">
         <is>
-          <t>A3 | 298呎 (1房)
+          <t>A3 | 299呎 (1房)
 $735万
-$24,669/呎
+$24,586/呎
 (24年-11月-11日)</t>
         </is>
       </c>
@@ -62689,9 +62689,9 @@
       </c>
       <c r="E31" s="22" t="inlineStr">
         <is>
-          <t>A3 | 298呎 (1房)
+          <t>A3 | 299呎 (1房)
 $731万
-$24,546/呎
+$24,464/呎
 (24年-11月-08日)</t>
         </is>
       </c>
@@ -63259,9 +63259,9 @@
       </c>
       <c r="E36" s="22" t="inlineStr">
         <is>
-          <t>A3 | 298呎 (1房)
+          <t>A3 | 299呎 (1房)
 $656万
-$21,997/呎
+$21,923/呎
 (24年-10月-28日)</t>
         </is>
       </c>
@@ -63381,9 +63381,9 @@
       </c>
       <c r="F37" s="22" t="inlineStr">
         <is>
-          <t>A5 | 298呎 (1房)
+          <t>A5 | 299呎 (1房)
 $577万
-$19,357/呎
+$19,292/呎
 (24年-11月-01日)</t>
         </is>
       </c>
@@ -63838,9 +63838,9 @@
       </c>
       <c r="Q7" s="22" t="inlineStr">
         <is>
-          <t>E | 468呎 (2房)
+          <t>E | 469呎 (2房)
 $1018万
-$21,755/呎
+$21,709/呎
 (24年-11月-06日)</t>
         </is>
       </c>
@@ -64053,9 +64053,9 @@
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>A | 908呎 (4+房)
+          <t>A | 909呎 (4+房)
 $3032万
-$33,398/呎
+$33,361/呎
 (24年-11月-15日)</t>
         </is>
       </c>
@@ -64190,9 +64190,9 @@
       </c>
       <c r="R11" s="22" t="inlineStr">
         <is>
-          <t>F | 461呎 (2房)
+          <t>F | 460呎 (2房)
 $1013万
-$21,972/呎
+$22,020/呎
 (24年-11月-19日)</t>
         </is>
       </c>
@@ -64440,9 +64440,9 @@
       </c>
       <c r="Q14" s="22" t="inlineStr">
         <is>
-          <t>E | 468呎 (2房)
+          <t>E | 469呎 (2房)
 $1030万
-$22,013/呎
+$21,966/呎
 (24年-11月-06日)</t>
         </is>
       </c>
@@ -64607,9 +64607,9 @@
       </c>
       <c r="E16" s="22" t="inlineStr">
         <is>
-          <t>A3 | 298呎 (1房)
+          <t>A3 | 299呎 (1房)
 $766万
-$25,696/呎
+$25,610/呎
 (24年-11月-01日)</t>
         </is>
       </c>
@@ -65199,9 +65199,9 @@
       </c>
       <c r="M21" s="22" t="inlineStr">
         <is>
-          <t>B6 | 237呎 (开放式)
+          <t>B6 | 236呎 (开放式)
 $544万
-$22,950/呎
+$23,047/呎
 (24年-11月-05日)</t>
         </is>
       </c>
@@ -65463,9 +65463,9 @@
       </c>
       <c r="E24" s="22" t="inlineStr">
         <is>
-          <t>A3 | 298呎 (1房)
+          <t>A3 | 299呎 (1房)
 $731万
-$24,538/呎
+$24,456/呎
 (24年-10月-28日)</t>
         </is>
       </c>
@@ -65734,9 +65734,9 @@
       </c>
       <c r="M26" s="22" t="inlineStr">
         <is>
-          <t>B6 | 237呎 (开放式)
+          <t>B6 | 236呎 (开放式)
 $537万
-$22,655/呎
+$22,751/呎
 (24年-11月-05日)</t>
         </is>
       </c>
@@ -65948,9 +65948,9 @@
       </c>
       <c r="M28" s="22" t="inlineStr">
         <is>
-          <t>B6 | 237呎 (开放式)
+          <t>B6 | 236呎 (开放式)
 $535万
-$22,565/呎
+$22,661/呎
 (24年-11月-06日)</t>
         </is>
       </c>
@@ -66269,9 +66269,9 @@
       </c>
       <c r="M31" s="22" t="inlineStr">
         <is>
-          <t>B6 | 237呎 (开放式)
+          <t>B6 | 236呎 (开放式)
 $531万
-$22,408/呎
+$22,503/呎
 (24年-11月-05日)</t>
         </is>
       </c>
@@ -66640,9 +66640,9 @@
       </c>
       <c r="E35" s="22" t="inlineStr">
         <is>
-          <t>A3 | 298呎 (1房)
+          <t>A3 | 299呎 (1房)
 $683万
-$22,906/呎
+$22,829/呎
 (24年-11月-20日)</t>
         </is>
       </c>
